--- a/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 13,7</t>
+          <t>-17,42; 13,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 27,7</t>
+          <t>-18,04; 23,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 24,05</t>
+          <t>-20,71; 25,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 177,55</t>
+          <t>-68,58; 157,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 339,63</t>
+          <t>-58,67; 297,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,61; 253,14</t>
+          <t>-58,8; 254,06</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 20,38</t>
+          <t>-5,38; 20,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 13,63</t>
+          <t>-14,93; 14,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 39,83</t>
+          <t>-7,52; 37,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 402,26</t>
+          <t>-36,83; 354,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 79,2</t>
+          <t>-47,68; 84,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 356,35</t>
+          <t>-47,94; 422,07</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 5,87</t>
+          <t>-14,45; 5,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 0,77</t>
+          <t>-26,71; 1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 10,7</t>
+          <t>-30,55; 11,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 180,98</t>
+          <t>-100,0; 226,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 30,09</t>
+          <t>-92,92; 38,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,8; 114,75</t>
+          <t>-85,65; 115,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,26; -0,4</t>
+          <t>-25,86; 0,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 9,83</t>
+          <t>-19,87; 9,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 8,65</t>
+          <t>-24,38; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,56; 12,1</t>
+          <t>-89,27; 8,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 118,64</t>
+          <t>-80,52; 101,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,24; 64,04</t>
+          <t>-73,53; 63,94</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 3,51</t>
+          <t>-9,76; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,18</t>
+          <t>-11,55; 3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 9,54</t>
+          <t>-10,16; 10,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 31,75</t>
+          <t>-52,47; 30,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 26,03</t>
+          <t>-45,9; 24,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 64,24</t>
+          <t>-45,17; 72,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 13,95</t>
+          <t>-16,8; 12,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 23,03</t>
+          <t>-15,11; 25,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 25,51</t>
+          <t>-20,24; 23,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 157,75</t>
+          <t>-69,75; 145,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,67; 297,39</t>
+          <t>-58,62; 298,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 254,06</t>
+          <t>-59,0; 273,25</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 20,45</t>
+          <t>-5,45; 18,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 14,23</t>
+          <t>-17,84; 11,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 37,36</t>
+          <t>-6,95; 45,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 354,22</t>
+          <t>-36,5; 325,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 84,34</t>
+          <t>-54,71; 64,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 422,07</t>
+          <t>-46,2; 471,34</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 5,76</t>
+          <t>-14,74; 5,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 1,18</t>
+          <t>-24,5; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 11,14</t>
+          <t>-24,25; 11,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,91</t>
+          <t>-100,0; 177,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,92; 38,89</t>
+          <t>-100,0; 51,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,65; 115,2</t>
+          <t>-83,69; 137,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 0,01</t>
+          <t>-24,6; -0,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 9,27</t>
+          <t>-19,05; 10,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 8,78</t>
+          <t>-23,76; 8,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 8,42</t>
+          <t>-87,48; 10,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 101,13</t>
+          <t>-77,0; 126,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 63,94</t>
+          <t>-74,44; 66,71</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,44</t>
+          <t>-9,87; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,97</t>
+          <t>-11,43; 4,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 10,82</t>
+          <t>-11,78; 9,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 30,8</t>
+          <t>-51,33; 29,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 24,54</t>
+          <t>-45,24; 32,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 72,56</t>
+          <t>-49,8; 63,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 12,92</t>
+          <t>-18,59; 13,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 25,47</t>
+          <t>-15,02; 27,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 23,37</t>
+          <t>-18,66; 24,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 145,88</t>
+          <t>-72,79; 177,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,62; 298,67</t>
+          <t>-55,61; 339,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 273,25</t>
+          <t>-59,93; 274,35</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 18,77</t>
+          <t>-5,43; 20,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 11,32</t>
+          <t>-16,04; 13,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 45,08</t>
+          <t>-10,99; 13,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 325,32</t>
+          <t>-36,67; 402,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 64,97</t>
+          <t>-51,59; 79,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 471,34</t>
+          <t>-64,13; 134,54</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,95%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 5,75</t>
+          <t>-13,74; 5,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 2,22</t>
+          <t>-25,08; 0,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 11,97</t>
+          <t>-20,6; 16,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 177,64</t>
+          <t>-100,0; 180,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,72</t>
+          <t>-92,17; 30,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 137,2</t>
+          <t>-63,12; 194,77</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,23</t>
+          <t>-8,41</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,57%</t>
+          <t>-33,25%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,6; -0,4</t>
+          <t>-25,26; -0,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 10,43</t>
+          <t>-20,7; 9,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 8,01</t>
+          <t>-24,44; 8,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 10,59</t>
+          <t>-87,56; 12,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 126,39</t>
+          <t>-77,32; 118,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 66,71</t>
+          <t>-71,84; 67,24</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,15</t>
+          <t>-9,31; 3,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 4,8</t>
+          <t>-12,21; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 9,51</t>
+          <t>-8,81; 8,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 29,91</t>
+          <t>-50,93; 31,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 32,38</t>
+          <t>-49,56; 26,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 63,97</t>
+          <t>-37,61; 58,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,6 +524,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,43 +542,55 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -582,6 +605,8 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -594,239 +619,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,76</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-13,05%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4049305073943348</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.202726791935496</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.076038631340231</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="n">
+        <v>-0.1040965816857776</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3903638035413447</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.2512704257521257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-18,59; 13,7</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-15,02; 27,7</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-18,66; 24,15</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-72,79; 177,55</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-55,61; 339,63</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-59,93; 274,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-4.329297061762852</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.415151035787411</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.266777135055809</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.7479492299912561</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.571362191889014</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.625063356230627</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>3.205585635446166</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.140908104088115</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.997685254885353</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>1.67413991159068</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>4.165267424742738</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.157826008363553</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,59</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55,62%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-6,01%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,43; 20,38</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-16,04; 13,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 13,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-36,67; 402,26</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-51,59; 79,2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-64,13; 134,54</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.6200963322040377</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.402444980941148</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2537811546811153</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3287612948149651</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.6534063268436199</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.6573806081601395</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.05592896237123746</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.09909854233858861</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,74</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-11,58</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-39,37%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-62,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.88749577348753</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.352453407039232</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.970722225459121</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.878656163334131</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.4735177840009082</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5073967940364728</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.679730164144785</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,74; 5,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-25,08; 0,77</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-20,6; 16,95</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 180,98</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-92,17; 30,09</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-63,12; 194,77</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3654199987168745</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.811699576298397</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.648358126328069</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.66491855998335</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>3.082099021860171</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.303872416764014</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.282567018062641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +805,279 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-12,03</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,41</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-58,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-26,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-33,25%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4325396864124835</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.7818458609901624</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.862744312890274</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.555894647678196</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.390323174367918</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.6070193418612945</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2885363847238691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-25,26; -0,4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-20,7; 9,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-24,44; 8,55</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-87,56; 12,1</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-77,32; 118,64</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-71,84; 67,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.904845627104155</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.051498487712432</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.676119858358108</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.867877232015758</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.9268016392191887</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7316231620151593</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.263444098450615</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3964518890834181</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.558547845451526</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>2.263975451262933</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5383600192859493</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.681844899093008</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.907666289545713</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.5308786320487937</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.704943287442064</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="n">
+        <v>-0.634762032911215</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2105490284690039</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3621317581142024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>-5.886866082516481</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.998600491322301</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.6864974060463</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.8987196950990138</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.8054114069784982</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7886241736759732</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>-0.1829300712550598</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.941830079710901</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.413737282083451</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>0.1627724601560926</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.75878720517285</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.6339642370363433</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-20,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-16,33%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,31; 3,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,21; 4,18</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,81; 8,33</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-50,93; 31,75</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-49,56; 26,03</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-37,61; 58,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.2738856552988349</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.671507957350739</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2862626670039708</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1027005476458086</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.743957402254015</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.213964349385178</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0851358743937965</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.02373919615862251</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.7410397768558225</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.981662512349796</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.798007706109021</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.214297346710313</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.518063506707691</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4405694074125874</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4080542466345386</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.09889020852468666</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.688386544041087</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.154712266141316</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.174077010630274</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>0.3343716630701448</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.4380421475230336</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.6609020978747435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -992,14 +1085,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
